--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H975"/>
+  <dimension ref="A1:H976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35888,6 +35888,64 @@
         </is>
       </c>
     </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>916251</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>有不動產經紀人員資格，就可以自己接案嗎？</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916251</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:51:18</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>不動產經紀人員資格</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>取得不動產經紀人或經紀營業員資格之後，是否就能以個人名義在租屋網站刊登物件、替屋主接聽電話、安排看屋，甚至在成交後收取服務費？
+答案是否定的。新北市政府於民國115年6月作成一則相當值得不動產經紀人考生注意的訴願決定。當事人雖具備「不動產經紀人員資格」，卻沒有任職於合法設立的不動產經紀業，而以個人名義在租屋網站反覆刊登34筆出租廣告，最終遭裁處10萬元罰鍰並禁止營業，提起訴願後仍遭駁回。這個案例把經紀人考試中幾個很容易混淆的觀念一次串了起來：「有證照」與「可以經營經紀業」，其實是兩件完全不同的事。
+• 一、案例事實
+本案起因於民眾向新北市政府地政局陳情，發現有人在租屋網站刊登出租廣告，但廣告中沒有合法經紀業名稱，而是留下個人的聯絡資訊。
+主管機關進一步查核後發現，該名訴願人雖具有不動產經紀人員資格，卻沒有任職於經主管機關許可的不動產經紀業；而且並非偶爾替一位朋友刊登一次廣告，而是在租屋網站上累計刊登了34筆出租廣告。此外，訴願人還與多位屋主或屋主親友簽有委託刊登出租授權書。
+這些廣告不只是單純寫上地址、租金而已，內容還介紹物件條件、周邊生活機能及交通情形，並留下訴願人自己的聯絡電話。更關鍵的是，部分廣告載明：「若有合意要租，酌收半個月服務費。」
+訴願人則主張，自己只是因為部分屋主年長、不熟悉網路操作，或屋主不希望直接接到大量詢問電話，所以才幫忙刊登資訊及轉達看屋需求；真正的租金、出租條件及最後是否出租，都還是由屋主決定。她也主張自己沒有實際收取仲介費，沒有設立公司，也沒有真正從事仲介業。
+但地政局並未接受這套說法，而是認定其已屬「非經紀業而經營仲介業務」，依不動產經紀業管理條例第32條第1項，裁處10萬元罰鍰並禁止營業。訴願人不服提起訴願，新北市政府最後仍決定「訴願駁回」。
+• 二、證照僅是「從業資格」
+取得不動產經紀人員資格，只代表具備從事相關專業工作的資格，並不代表可以脫離合法經紀業，以個人名義自行經營仲介或代銷業務。
+不動產經紀業管理制度並不是只要求「負責接案的人有證照」，而是建立一整套交易安全機制，包括主管機關許可、公司或商業登記、營業保證金、加入同業公會以及配置法定經紀人員等。因此，本案即使當事人有不動產經紀人員資格，也無法取代「經紀業」本身必須完成的法定程序。
+反覆刊登34筆出租物件、留下自己的聯絡方式、替出租人與承租人傳遞資訊，又載明成交時可能收取半個月服務費，整體行為已經不是單純幫忙，而具有公開招攬、媒合及持續經營仲介業務的客觀表徵，因此最後維持10萬元罰鍰及禁止營業的處分。
+• 三、經紀人考試應注意之處
+這個案例很適合拿來準備「不動產經紀相關法規概要」。考前至少要掌握以下幾個容易被命題老師設計成陷阱的觀念：
+• (一) 經紀業、經紀人、經紀營業員是不同概念：經紀業是依法經營仲介或代銷業務的公司或商號；經紀人與經紀營業員則屬「經紀人員」。不要因為取得個人證照，就誤以為可以獨立以個人名義開業。
+• (二) 仲介包括買賣、互易、租賃的居間或代理：居間不只是「在雙方中間殺價、談條件」，單純報告訂約機會，也可能具有居間性質。
+• (三) 是否實際收取服務費，並非行政管制上唯一判斷標準：不要看到題目寫「沒有成交」、「尚未收到佣金」就直接選擇「不構成仲介」。仍要觀察其是否已公開招攬、媒合，以及是否具有繼續反覆經營的情形。
+• (四) 經營業務重點在「繼續、反覆實施」：本案34筆廣告就是非常典型的判斷素材；但考試時也不要死背「一定要幾筆」，法律並沒有規定刊登到第幾筆才算經營，仍須依個案整體事實判斷。
+• (五) 非經紀業經營仲介或代銷業務之處分：禁止營業＋10萬元以上30萬元以下罰鍰。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H976"/>
+  <dimension ref="A1:H977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35946,6 +35946,50 @@
         </is>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>916280</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>土地法第73條之1優先購買權之實例研習</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>2026/09/17</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916280</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:49:55</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>土地法、優先購買權</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>甲、乙二人共有一筆土地，應有部分各二分之一。二人並訂定分管契約，約定各自使用一半土地。甲之分管部分，一半出租於丙建屋使用，不久丙即建屋使用；一半出借於丁建屋使用，不久丁亦建屋使用。之後，甲死亡，繼承人戊一直未辦理繼承登記，經財政部國有財產署公開標售，並由庚得標。試問何人有優先購買權？
+【解答】
+• (一) 承租人丙為合法使用人，就其使用範圍部分得主張優先購買。借用人丁為合法使用人，就其使用範圍部分得主張優先購買。經優先購買後，該地產權為乙應有部分二分一，丙應有部分四分之一，丁應有部分四分之一。
+• (二) 戊為繼承人，其優先購買順序先於合法使用人，但繼承人無使用範圍，故無優先購買權。
+• (三) 乙依據土地法第34條之1第4項主張優先購買權。然，依「逾期未辦理繼承登記土地及建築改良物標售作業要點」第13點規定，土地法第73條之1第3項之優先購買權與其他法律規定之優先購買權競合時，應優先適用土地法第73條之1之優先購買權。故丙、丁之優先購買權先於乙而行使。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H977"/>
+  <dimension ref="A1:H980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35990,6 +35990,159 @@
         </is>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>916315</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>公共設施保留地之相關限制與保障</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916315</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:53:51</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>公共設施保留地、都市計畫法、地價稅、土地增值稅、房地合一</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>甲所有一筆位於A市都市計畫區內之土地，原有合法建物供營業使用。民國84年都市計畫通盤檢討時，該土地被劃定為「公園用地」，預定未來由A市政府取得興闢公園，但因地方財政等因素，三十年來始終未辦理取得。
+在此期間，甲仍繼續原有營業使用，後來曾打算拆除舊建物改建三層樓商場，但因可能妨礙將來公園之興闢而未獲准許。其後甲停止營業並拆除原有建物，土地未作任何使用，且與其他使用中土地隔離。
+到了民國114年，甲認為土地被劃為公園用地已約30年，主張都市計畫既以25年為規劃年期，政府超過25年仍未取得，土地應自動解除公共設施保留地之限制。因政府否認其主張，甲遂考慮將土地出售予乙。
+數年後，A市政府最終決定興建公園並辦理徵收。此時該公園用地本身因長期受到使用限制，市場價格明顯低於附近住宅區土地。究竟甲在公共設施保留期間得如何使用土地？超過25年是否自動解編？持有、出售及最後遭徵收時，又有哪些特別規定？
+• 一、相關法規
+• (一) 公共設施保留地之使用限制
+依都市計畫法第51條規定：「依本法指定之公共設施保留地，不得為妨礙其指定目的之使用。但得繼續為原來之使用或改為妨礙目的較輕之使用。」
+因此，甲原來合法存在之使用原則上仍得繼續，但不能因政府尚未取得，即進行足以妨礙未來公園興闢之新開發。
+另依都市計畫法第50條規定：「公共設施保留地在未取得前，得申請為臨時建築使用。」「前項臨時建築之權利人，經地方政府通知開闢公共設施並限期拆除回復原狀時，應自行無條件拆除；其不自行拆除者，予以強制拆除。」
+故公共設施保留地並非完全不能利用，仍得依規定申請臨時建築，但日後政府開闢公共設施時，應依規定拆除。
+• (二) 超過25年未取得之效果
+依都市計畫法第5條規定，都市計畫係「預計二十五年內之發展情形」訂定；惟司法院釋字第336號已指出，此25年係都市計畫之規劃考量期間，並非公共設施保留地之法定取得期限，除非依法辦理都市計畫變更，並不因25年期間經過而當然解除。
+另按都市計畫法第50條之2第1項規定：「私有公共設施保留地得申請與公有非公用土地辦理交換，不受土地法、國有財產法及各級政府財產管理法令相關規定之限制；劃設逾二十五年未經政府取得者，得優先辦理交換。」
+因此，25年並不是公共設施保留地之「自動解編期限」。而就公共設施保留地之土地交換而言，都市計畫法第50條之2明定，劃設超過25年仍未經政府取得者，於申請與公有非公用土地交換時得優先辦理。
+• (三) 保留期間之地價稅
+依土地稅法第19條規定：「都市計畫公共設施保留地，在保留期間仍為建築使用者，除自用住宅用地依第十七條之規定外，統按千分之六計徵地價稅；其未作任何使用並與使用中之土地隔離者，免徵地價稅。」
+換言之，公共設施保留地並非一律免徵地價稅。甲仍以原建築物營業使用期間，原則上適用千分之六稅率；嗣後如確實未作任何使用，且與使用中土地隔離，始得適用免徵規定。
+• (四) 出售公共設施保留地之土地增值稅與房地合一所得稅
+依土地稅法第39條第2項規定：「依都市計畫法指定之公共設施保留地尚未被徵收前之移轉，準用前項前段規定，免徵土地增值稅。」
+本案甲若在該土地仍為公共設施保留地且尚未被徵收前出售予乙，原則上得適用免徵土地增值稅之規定。不過，同項後段亦規定，土地日後如變更為非公共設施保留地再移轉，仍應依第一次免徵土地增值稅前之原規定地價，或最近一次課徵土地增值稅時核定之申報移轉現值為原地價，計算漲價總數額。
+另依所得稅法第4條之5第1項第4款規定，尚未被徵收前移轉依都市計畫法指定之公共設施保留地，如屬房地合一課稅範圍，免納所得稅。
+• (五) 政府最後徵收時之地價補償
+依土地徵收條例第30條第1項規定：「被徵收之土地，應按照徵收當期之市價補償其地價。在都市計畫區內之公共設施保留地，應按毗鄰非公共設施保留地之平均市價補償其地價。」
+因此，都市計畫區內公共設施保留地遭徵收時，並非直接依該土地因長期受管制而降低後之市場價格補償，也不是以公告土地現值作為現行補償標準，而應按毗鄰非公共設施保留地之平均市價補償。
+應特別注意，都市計畫法第49條目前仍有以毗鄰非公共設施保留地「平均公告土地現值」補償之文字。惟依土地徵收條例第1條第3項規定，其他法律有關徵收補償標準與土地徵收條例牴觸者，優先適用土地徵收條例。因此，現行補償標準應依土地徵收條例第30條，以毗鄰非公共設施保留地之平均「市價」為準。
+• 二、結論
+本案甲之土地經都市計畫劃定為公園用地，預定由政府取得，而在政府尚未依法取得前，即處於公共設施保留之狀態。甲雖仍保有土地所有權，但所有權之使用受到都市計畫限制，不得進行妨礙未來公園興闢之使用。至於原有合法使用則得繼續，亦得依法申請臨時建築。
+其次，甲主張公園用地劃設超過25年即應自動解編，並不正確。25年並非自動解編期限，而是申請土地交換時的重要優先條件。至於公共設施是否仍有保留必要，仍應透過都市計畫通盤檢討及法定變更程序處理，而非因時間經過自動改變土地使用性質。
+在租稅方面，甲如仍將該公共設施保留地作建築使用時，地價稅原則按千分之六計徵，只有在未作任何使用且與使用中土地隔離時，才得免徵地價稅。若甲不願繼續等待政府取得而將土地出售，在仍屬公共設施保留地且尚未被徵收的情形下，則得免徵土地增值稅。另應注意，如題目改為105年1月1日以後取得之公共設施保留地，而屬所得稅法第4條之4所定房地合一課稅範圍者，依同法第4條之5第1項第4款規定，尚未被徵收前移轉，免納所得稅。
+最後，政府真正決定興闢公園並辦理徵收時，依現行土地徵收條例，都市計畫區內公共設施保留地應按毗鄰非公共設施保留地之平均市價補償，而非逕以該公園用地受到長期使用限制後已降低之交易價格計算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>916314</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>重劃後第一次移轉減徵40%土地增值稅之原則與例外(二)</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>2026/10/01</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916314</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:53:57</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>不課徵土地增值稅、贈與其配偶、移轉第三人</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>土地稅法第39條之1第1項規定：「經重劃之土地，於重劃後第一次移轉時，其土地增值稅減徵百分之四十。」土地重劃後配回之土地，贈與其配偶，再移轉第三人，可否減徵40%？茲分下列二種情形說明：
+• (一) 贈與其配偶申請不課徵土地增值稅：「贈與其配偶」屬於第一次移轉，「再移轉第三人」屬於第二次移轉。然，贈與其配偶時，申請不課徵土地增值稅。因「不課徵」屬於租稅遞延，應負擔之土地增值稅並未減少，故於再移轉第三人時，如未予減徵40%，顯然違反平等原則。因此，「再移轉第三人」雖屬第二次移轉，仍得適用減徵40%。
+• (二) 贈與其配偶未申請不課徵土地增值稅：贈與其配偶時，未申請不課徵土地增值稅，此際應課徵土地增值稅，並給予減徵40%。之後，「再移轉第三人」屬於第二次移轉，就不得再適用減徵40%。換言之，「贈與其配偶」屬於第一次移轉，「再移轉第三人」屬於第二次移轉。第一次移轉已減徵40%，第二次移轉不得再減徵40%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>916313</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>重劃後第一次移轉減徵40%土地增值稅之原則與例外(一)</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916313</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:54:04</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>土地增值稅、贈與其配偶</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>土地稅法第39條之1第1項規定：「經重劃之土地，於重劃後第一次移轉時，其土地增值稅減徵百分之四十。」所稱移轉，包括買賣、贈與及繼承等。茲舉「贈與配偶」及「繼承」二種特殊情形說明：
+• (一) 贈與配偶：土地重劃後配回之土地，贈與其配偶，再移轉第三人。「贈與其配偶」屬於第一次移轉，「再移轉第三人」屬於第二次移轉。然，贈與其配偶時，申請不課徵土地增值稅。因「不課徵」屬於租稅遞延，應負擔之土地增值稅並未減少，故於再移轉第三人時，如未予減徵40%，顯然違反平等原則。因此，「再移轉第三人」雖屬第二次移轉仍得適用減徵40%。
+• (二) 繼承：土地重劃後配回之土地，先發生繼承，再移轉第三人。繼承而移轉土地，免徵土地增值稅。因「免徵」屬於租稅免除，所享受之租稅優惠遠較減徵40%為多，故於再移轉於第三人時，不得再減徵40%。換言之，「繼承」屬於第一次移轉，「再移轉第三人」屬於第二次移轉，第二次移轉不得減徵40%。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H980"/>
+  <dimension ref="A1:H982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36143,6 +36143,108 @@
         </is>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>916366</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>房子持有近20年，為何房地合一稅仍課35%？—夫妻贈與與剩餘財產分配的取得日認定</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916366</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:33:20</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>房地合一稅、夫妻贈與、剩餘財產</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各位同學好
+本週專欄整理一個房地合一所得稅的訴願案，其涉及夫妻贈與+剩餘財產差額分配之取得日認定觀念，非常值得瞭解及釐清觀念，茲整理如下：
+• (一) 主要爭點 A於94年買入→ A於108年贈與配偶B → A、B離婚 → B於109因剩餘財產分配將房地移轉回A → A於113年出售。
+[圖片1]
+就外觀而言，自A於94年取得，至A113年出售，持有近20年，故A主張：
+1. 系爭房地原係A於94年買賣取得，雖經贈與B後再因剩餘財產差額分配移回A，仍應以A於94年原始取得日為取得日，適用舊制房屋交易損益規定。
+2. 縱使無舊制適用，也應以夫妻持有系爭房地期間合併計算，而適用新制持有10年以上的15%稅率。
+• (二) 重要規定 首先，要先注意兩個規定：
+1. 財政部106年3月2日台財稅字第10504632520號令：「個人取得配偶贈與之房屋、土地，適用遺產及贈與稅法第20條第1項第6款配偶相互贈與之財產不計入贈與總額規定者，出售時應以配偶間第1次相互贈與前配偶原始取得該房屋、土地之日為取得日，據以計算持有期間及認定應適用所得稅法第14條第1項第7類規定計算房屋之財產交易損益(以下簡稱舊制房屋交易損益)或依同法第14條之4規定計算個人房屋、土地交易所得或損失(以下簡稱新制房屋土地交易損益)，並按該房屋、土地原始取得之原因，分別依所得稅法相關規定課徵所得稅。」
+2. 房地合一稅申報作業要點（以下簡稱申報要點）第4點第13款有關房屋、土地取得日之認定：「配偶之一方依民法第1030條之1規定行使剩餘財產差額分配請求權取得之房屋、土地、房屋使用權、預售房地、股份或出資額，為配偶之他方原取得之日。」
+• (三) 訴願決定理由 按民法第406條規定，贈與係基於當事人雙方合意，一方以自己之財產無償給與他方，他方允受之契約；同法第1030條之1規範之夫妻剩餘財產分配請求權，乃夫妻婚姻關係消滅時，由財產少的一方對多的一方請求分配差額，係為債權的行使。由此觀之，前者為契約行為，後者屬單獨行為。復按同法第1018條規定，夫或妻各自管理、使用、收益及處分其財產，且我國夫妻財產制係採分別財產制為基礎之「法定財產制」，並無將夫妻財產逕視為同一經濟實體之法律基礎(最高行政法院104年度判字第129號判決參照)。所訴夫妻為同一經濟實體，應以訴願人原始取得系爭房地之日為取得日，適用舊制房屋交易損益一節，容難採據。
+• (四) 曾老師整理說明 首先，本案財政部區分「因配偶贈與取得」與「因剩餘財產差額分配取得」二種取得原因。 其次，倘若94年A買入房地，108年A贈與配偶B，而B嗣後直接出售，在符合遺產及贈與稅法第20條第1項第6款規定之前提下，依財政部106年令，其取得日得回溯至夫妻第一次相互贈與前A於94年的原始取得日，因此就新舊制判斷而言，原則上適用舊制房屋交易損益規定。 然而，此案是B並未出售，而是於109年又因剩餘財產分配移轉回給A，由A再次取得，並由A於113年出售，因而A出售時的取得日，係屬剩餘財產差額分配，故依據前述申報要點規定，係以配偶他方B的原取得日，也就是A於108年贈與給B時。 同時，本案A係因夫妻剩餘財產分配取得系爭房地，與106年令所規範之「因配偶贈與取得」要件不同，故不得再援引106年令，將取得日從108年第二次向前回溯至A於94年的原始取得日。
+[圖片2]
+• (五) 結果 依申報要點認定，A之稅法上取得日為108年8月20日，至113年4月29日出售時，稅法上持有期間超過2年、未逾5年，故適用35%稅率。
+## 文章圖片
+![圖片1](./images/916366_67bf9aff.png)
+![圖片2](./images/916366_f2522a1c.png)
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>916350</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>收回房屋之法規適用</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916350</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:33:27</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>收回房屋、土地法、租賃專法</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>由於收回房屋之規定有民法、土地法及租賃住宅市場發展及管理條例（下稱租賃專法），其相互規範有所重疊，其適用情形，整理說明如下：
+1. 民法係做一般性租賃物規範。
+2. 土地法針對房屋予以特別規定，並屬強制規範，而不得特約排除。
+3. 租賃專法針對租賃住宅又為土地法及民法之特別法，如有相同規定則優先適用，倘若租賃專法未規定，則仍可適用土地法及民法。
+茲將各法規有關出租人收回房屋之規定彙整如下表所示：
+• T. ABLE_PLACEHOLDER_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H982"/>
+  <dimension ref="A1:H983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36245,6 +36245,54 @@
         </is>
       </c>
     </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>916375</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>私契與公契</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916375</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:07:37</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>私契、公契、債權契約、物權契約</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>不動產契約書分為私契與公契二種。一般而言，法條皆以「契約」或「契約書」規定，不會明文規定私契或公契。然，實務應用時，應判斷此契約是屬於私契，抑或公契。
+• (一) 私契：當事人互相表示意思一致，並記載於書面，即是私契。私契為債之發生原因，因此私契之法律性質為債權契約。其作用在當事人履行契約有所依據，以避免對方反悔。下列法條之契約或契約書，指私契而言。
+1. 契約以負擔不動產物權之移轉、設定或變更之義務為標的者，應由公證人作成公證書。未依前項規定公證之契約，如當事人已合意為不動產物權之移轉、設定或變更而完成登記者，仍為有效（民§166-1）。 上開所稱契約，指私契。換言之，應對私契加以公證，而非對公契加以公證。其目的在減少不動產糾紛，預防訴訟之舉證困難。惟本法條之施行日期，由行政院會同司法院另定之（民債施§36Ⅱ）。施行日期至今尚未訂定，因此本法條尚未施行。
+2. 個人有房屋、土地之交易所得或損失，不論有無應納稅額，應於下列各款規定日期起算三十日內自行填具申報書，檢附契約書影本及其他有關文件，向該管稽徵機關辦理申報；其有應納稅額者，應一併檢附繳納收據（所§14-5前段）。 上開所稱契約書，指私契。換言之，房地合一所得稅之納稅義務人申報房地交易所得或損失，應檢附記載實際交易價格之私契影本。
+• (二) 公契：指公定契約書：公契之法源為民法第758條第2項。亦即，不動產物權依法律行為而取得、設定、喪失及變更者，非經登記，不生效力（民§758Ⅰ）。前項行為，應以書面為之（民§758Ⅱ）。因此公契之法律性質為物權契約。公契之作用在登記機關進行土地登記時，有所依據。下列法條之契約或契約書，指公契而言。
+1. 登記機關應備下列登記書表簿冊圖狀：(1)登記申請書；(2)登記清冊；(3)契約書；(4)收件簿；(5)土地登記簿及建物登記簿；(6)土地所有權狀及建物所有權狀；(7)他項權利證明書；(8)地籍圖；(9)地籍總歸戶冊（卡）；(10)其他必要之書表簿冊（登§14）。 上開所稱契約書，指公契。換言之，公契由登記機關訂定格式，私契無一定格式。
+2. 土地所有權移轉或設定典權時，權利人及義務人應於訂定契約之日起三十日內，檢同契約及有關文件，共同申請土地所有權移轉或設定典權登記，並共同申報其土地移轉現值。但依規定得由權利人單獨申請登記者，權利人得單獨申報其移轉現值。 上開所稱契約，指公契。換言之，土地增值稅之納稅義務人申報土地移轉現值時，應檢附公契。
+綜上，一筆不動產交易發生二個法律行為，一個為債權行為，因而有債權契約（即私契）；另一個為物權行為，因而有物權契約（即公契）。一般而言，債權行為發生在先，物權行為發生在後。
+【註】 民：民法。 民債施：民法債編施行法。 平：平均地權條例。 登：土地登記規則。 所：所得稅法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H983"/>
+  <dimension ref="A1:H984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36293,6 +36293,74 @@
         </is>
       </c>
     </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>916404</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>繼承合建分回的房屋，為何房地合一稅可從35%降為15%？—合建分屋與繼承之持有期間計算</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916404</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:38:52</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>合建分屋、房地合一稅</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各位同學好
+本週專欄整理一個最高行政法院有關房地合一所得稅的判決，其涉及「合建分屋＋繼承」之持有期間計算問題。究竟繼承人出售被繼承人與建商合建分得的房屋時，能否將被繼承人原有土地的持有期間一併計算？最高行政法院對此有重要見解，非常值得瞭解及釐清觀念，茲整理如下：
+• (一) 案例事實與爭點 90年4月4日，A因繼承取得土地 → 102年10月7日，A以該土地與建商簽約合建 → 106年9月4日，A因合建取得新建房屋 → 108年9月5日，A死亡，由子女B、C繼承房地 → 109年7月16日，B、C辦理分割繼承登記，各取得1/2 → 110年9月16日，B與另一共有人出售系爭房地，並於110年10月21日完成所有權移轉登記。
+[圖片1]
+本案房地出售總價為1,825萬元。其中，B出售其繼承取得的1/2持分，申報房地合一所得稅時，依持有期間超過10年，適用15%稅率，繳納稅額339,296元。然而，國稅局認為：
+1. 土地部分：A於90年4月4日取得原有土地，雖然後來參與合建，仍可認定為原有土地的延伸，適用舊制，土地交易所得免納所得稅。
+2. 房屋部分：A於106年9月4日才因合建取得新建房屋，B於108年9月5日繼承取得。因此，縱使合併A持有該房屋的期間，至110年10月21日出售時，仍屬持有超過2年、未逾5年，應適用35%稅率。
+因此核定B出售房屋的課稅所得為2,260,453元，按35%計算應納稅額791,158元，扣除原已繳納稅額後，要求補稅451,862元。
+綜上，本案主要爭點在於：B繼承的雖然是A於106年合建取得的房屋，但A原有土地早於90年即已取得，而且該土地亦係繼承而來。B能否主張，合建分屋本質上是原土地的替代或變形，故計算房屋持有期間時，應將A原有土地的持有期間，以及前手因繼承而可合併的期間，一併計算，適用超過10年的15%稅率？
+• (二) 重要規定
+1. 所得稅法第14條之4第4項：第4條之5第1項第1款及前項有關期間之規定，於繼承或受遺贈取得者，得將被繼承人或遺贈人持有期間合併計算。
+2. 房地合一課徵所得稅申報作業要點第5點第2項：依本案適用規定，個人出售以自有土地與其他營利事業合建分屋所取得的房屋，依所得稅法第14條之4第3項計算房屋持有期間時，應以該土地的持有期間為準。 換言之，地主以原有土地與建商合建分得房屋，雖然房屋是後來才興建完成，但計算房地合一稅持有期間時，並非一律以新建房屋的取得日為起算點，而得以原有土地的持有期間為準。
+3. 房地合一課徵所得稅申報作業要點第4點有關取得日之認定（本案行為時為第2款第7目、第9目；現行條文為第9款、第14款）：(1)原土地所有權人以自有土地與營利事業合建分屋，分配取得的土地，原則上以原取得合建前土地之日為取得日。(2)繼承取得的房屋、土地，以繼承開始日為取得日。
+4. 財政部112年11月2日台財稅字第11204619060號令：個人交易105年1月1日以後繼承或受遺贈取得的房地，依所得稅法第14條之4第4項計算持有期間，如屬連續繼承或受遺贈取得，得將連續各次繼承或受遺贈之被繼承人或遺贈人的持有期間合併計算。
+5. 財政部104年8月19日台財稅字第10404620870號令：交易之房屋、土地係被繼承人於104年12月31日以前取得，且納稅義務人於105年1月1日以後繼承取得者，以目的性限縮解釋排除適用新制。
+• (三) 法院判決理由
+1. 臺北高等行政法院111年度訴字第1314號判決 原審法院認為，A於106年9月4日因合建取得系爭房屋，B則於108年9月5日因繼承取得。依房地合一課徵所得稅申報作業要點第5點第1項第1款規定，B固然得合併計算被繼承人A的持有期間，但該期間應以A實際取得系爭房屋之日，即106年9月4日起算。 至於合建分屋可以原有土地持有期間計算之規定，原審認為係針對參與合建的地主本人，B並非原參與合建者，不能直接主張適用。因此，原審認定B出售系爭房屋的持有期間為超過2年、未逾5年，國稅局適用35%稅率並無違誤，判決駁回B之訴。
+2. 最高行政法院112年度上字第583號判決 最高行政法院則採取不同見解，其理由主要如下：(1)合建分得的房屋，具有原有土地替代或變形的性質 地主以自有土地與建商合建，通常係以部分土地交換建商興建完成的房屋。因此，合建所分得的房屋，實質上是以原有土地交換而來，具有原土地替代或變形的性質，學說上亦有稱為「代位物」者。基於此種性質，地主取得合建分回的房屋，並非短期炒作不動產，故計算房屋持有期間時，應以其原有土地的持有期間為準。(2)繼承人應得承受被繼承人的持有期間利益 所得稅法第14條之4第4項允許繼承人合併計算被繼承人的持有期間，係因繼承並非人為控制所得實現的行為，原則上不存在短期炒作房地產的疑慮。同時，依民法第1148條第1項及概括繼承法理，繼承人原則上承受被繼承人財產上的權利義務，因此亦應得承受被繼承人生前持有房地的期間利益。(3)合建分屋與繼承的持有期間計算規定，應予結合適用 最高行政法院認為，雖然房地合一課徵所得稅申報作業要點未明定「地主合建分屋後死亡，由繼承人出售該房屋」的持有期間應如何計算，但依所得稅法第14條之4第4項，以及申報作業要點第5點第1項第1款、第2項的規範意旨，應允許繼承人合併計算被繼承人原有土地的持有期間。因此，國稅局主張只有原地主本人出售合建分屋才能適用，而繼承人不得適用，與前述規範意旨不符，難以採納。
+• (四) 曾老師整理說明 首先，本案要區分「取得日」與「持有期間」二個不同的概念。本案A原有土地於90年4月4日繼承取得，而合建分得的房屋則於106年取得。嗣後B於108年因繼承取得系爭房屋，故B在稅法上的房屋取得日，仍為108年9月5日的繼承開始日。 然而，房屋取得日為108年，並不代表計算持有期間時，只能從108年起算。其次，如果A於106年取得合建分回的房屋後自行出售，依申報作業要點第5點第2項規定，計算房屋持有期間時，得以其原有土地的持有期間為準，也就是可以追溯至90年4月4日，而非僅從106年取得新建房屋時開始計算。 本案較特殊之處，在於A並未出售房屋，而是死亡後由B繼承，再由B出售。依最高行政法院見解，既然B是概括繼承A的財產，而A持有合建分屋的期間原本即可追溯至原有土地的持有期間，則B也應承受這項持有期間利益，不應因為A死亡、改由B繼承出售，就將持有期間重新限縮至106年取得房屋之日。 再者，本案A於90年取得原有土地，本身也是因繼承而來。最高行政法院並進一步參酌財政部112年令有關連續繼承持有期間得合併計算的意旨，認為尚得併計A於90年繼承土地以前，被繼承人的持有期間（此部分對本案結論並非必要，但顯示法院認為合建代位與連續繼承兩項規定可以疊加適用）。因此，本案在持有期間的計算，包含以下二個重要觀念，且二項規定可以結合適用，而非相互排斥：
+1. 合建分屋：以原有土地的持有期間計算新建房屋的持有期間。
+2. 繼承取得：繼承人得合併計算被繼承人的持有期間，並承受前述合建分屋所形成的期間利益。
+不過，仍須注意，本案最高行政法院並非認定B繼承取得的房屋可直接改按90年的取得日適用舊制。系爭房屋仍屬房地合一稅新制的課稅範圍，只是計算新制稅率所需的「持有期間」時，可以往前合併計算。
+[圖片2]
+• (五) 結果 最高行政法院認定，系爭房屋雖然是A於106年合建取得，B於108年繼承取得，但計算房地合一稅持有期間時，應合併計算A原有土地的持有期間，以及依法得併計的連續繼承期間。 依此計算，截至110年10月21日出售時，B的房屋持有期間已超過20年（單以A於90年4月4日取得原有土地起算，至110年10月21日出售時已逾20年；若再依112年令併計A繼承前被繼承人的持有期間，期間更長。無論如何均超過10年，適用15%稅率），符合所得稅法第14條之4第3項第1款第4目持有期間超過10年、適用15%稅率的規定，不必補繳451,862元。
+資料來源：最高行政法院114年2月12日112年度上字第583號判決；臺北高等行政法院111年度訴字第1314號判決
+## 文章圖片
+![圖片1](./images/916404_b3c3a6eb.png)
+![圖片2](./images/916404_71e65efa.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H984"/>
+  <dimension ref="A1:H985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36361,6 +36361,57 @@
         </is>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>916420</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>土地與建物之分開課稅與合併課稅</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>2026/10/15</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916420</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:55:42</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>土地與建物分開課稅、土地與建物合併課稅</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我國現行不動產稅，採用土地與建物分開課稅者，如地價稅、房屋稅、土地增值稅及契稅等。採用土地與建物合併課稅者，如房地合一所得稅。
+• (一) 土地與建物分開課稅之理由： 土地與建物之性質不同，土地價值隨時間經過而遞增，建物價值隨時間經過而遞減。如圖所示。因此，二者應分別訂價，分開課稅。是土地法第145條規定：「土地及其改良物之價值，應分別規定。」[圖片1] 土地與建物分開課稅之最大問題在無法採用實際市場價格或實際交易價格課稅。實務上，建物與其基地一併交易。然為了課稅，將房地實際交易價格強行拆分為土地價格及建物價格二部分；但難有合理拆分方法，造成土地價格及建物價格失真。因而現行皆採政府規定價格課稅。例如：
+1. 地價稅之稅基，源自公告地價。
+2. 房屋稅之稅基，源自房屋標準單價。
+3. 土地增值稅之稅基，源自公告土地現值。
+4. 契稅之稅基，源自房屋標準單價。
+採土地與建物分開課稅，易造成稅負不合理與不公平。茲舉一例說明，若出售房地發生虧損，但因公告土地現值調高，仍須繳納土地增值稅。
+• (二) 土地與建物合併課稅之理由： 基於建物與其基地一併交易，因此採實際交易價格課稅，無須再拆分為土地價格及建物價格。如房地合一所得稅即是。
+綜上，早期以土地與建物分開課稅為主流，晚近則以土地與建物合併課稅為主流。因此，最近有地價稅與房屋稅合併為「不動產稅」之倡議，即是一例。
+## 文章圖片
+![圖片1](./images/916420_c744aa54.png)
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H985"/>
+  <dimension ref="A1:H986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36412,6 +36412,92 @@
         </is>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>916448</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>死亡前2年內贈與併計遺產，受贈人改按比例負擔遺產稅</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916448</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>2026-10-20 15:58:58</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>遺產稅、擬制遺產、遺產及贈與稅法</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>一名年僅6歲的女童，實際繼承約1,567萬元遺產，卻遭國稅局核定高達5,735萬元的遺產稅！原因是父親生前將價值3億餘元的股票贈與配偶，死亡後配偶及其他子女均拋棄繼承，導致未取得該筆股票的女童，反而須承擔因股票併計遺產所產生的稅負。
+這起爭議最終促成憲法法庭113年憲判字第11號判決，並推動《遺產及贈與稅法》修正。
+總統於115年9月11日修正公布《遺產及贈與稅法》部分條文，其中一項重要變革，就是明定被繼承人死亡前2年內贈與特定親屬、依法併入遺產總額課稅之財產，其對應的遺產稅額應由受贈人按比例負擔，不再全部由繼承人承擔。亦即重新劃分生前受贈人與繼承人的納稅義務。
+此一修正對於不動產生前贈與、財產傳承與繼承稅務規劃，具有重要的實務意義。
+• 一、舊制問題：擬制遺產的稅，究竟由誰負擔？依《遺產及贈與稅法》第15條第1項規定，被繼承人死亡前2年內贈與下列個人之財產，應於死亡時視為被繼承人之遺產，併入遺產總額課稅：
+1. 被繼承人之配偶。
+2. 民法第1138條及第1140條規定之各順序繼承人。
+3. 前款各順序繼承人之配偶。
+此即一般所稱的「擬制遺產」，主要目的在防止被繼承人於死亡前透過贈與移轉財產，規避遺產稅負擔。
+惟應注意，財產被擬制為遺產，並不表示該財產在民法上重新成為被繼承人死亡時遺留的財產。擬制遺產係稅法上計算遺產總額的規定，與民法上的財產歸屬及繼承標的仍應區別。
+問題在於，修法前第6條第1項規定，有遺囑執行人者，以遺囑執行人為遺產稅納稅義務人；無遺囑執行人者，則以繼承人及受遺贈人為納稅義務人。受贈人並不因受贈該財產，即當然成為遺產稅納稅義務人。
+尤其配偶間相互贈與財產，依同法第20條第1項第6款規定，不計入贈與總額，因此可能發生：
+1. 被繼承人生前將鉅額財產贈與配偶，配偶不因該筆贈與負擔贈與稅。
+2. 被繼承人於贈與後2年內死亡，該筆財產依法併計遺產總額。
+3. 倘受贈配偶又拋棄繼承，即可能使其他繼承人須以其繼承之財產，負擔因配偶受贈財產而增加的遺產稅。
+換言之，取得財產者與負擔稅捐者並非同一人，形成租稅負擔與財產利益歸屬不一致的問題。
+• 二、修法緣由：113年憲判字第11號揭示兩項違憲爭議憲法法庭於113年10月28日公告113年憲判字第11號判決，涉及兩個不同層次的擬制遺產課稅問題。
+（一）受贈配偶與其他繼承人的遺產稅負擔不公平第一起案件中，陳姓被繼承人生前將價值3億餘元的股票贈與配偶，於贈與後2年內死亡。其配偶及三名婚生子女均拋棄繼承，最後由一名6歲非婚生女兒繼承遺產。該女童實際繼承財產約1,567萬元，但因前述股票須併入遺產總額，國稅局核定遺產稅高達5,735萬元。
+憲法法庭認為，死亡前2年贈與配偶之財產，雖得依法擬制為遺產課稅，但對於受贈配偶與其他繼承人應如何負擔遺產稅，法律欠缺明確規範，致其他繼承人須以其繼承之財產，就配偶受贈所產生的財產增益負擔稅捐，在此範圍內不符憲法第7條保障平等權之意旨。其使繼承人繼承權之經濟價值嚴重減損者，並侵害憲法第15條保障之財產權。
+（二）擬制遺產欠缺配偶剩餘財產差額分配請求權的相應扣除另一案件中，被繼承人於105年5月3日將土地贈與配偶，同年5月14日即死亡，死亡後該筆土地依法併入遺產總額課稅。然而，稅捐機關在計算配偶剩餘財產差額分配請求權扣除額時，並未相應將該筆擬制遺產納入計算，引發爭議。
+憲法法庭認為，法律既將死亡前2年贈與配偶之財產視為遺產課稅，卻欠缺相當於《遺產及贈與稅法》第17條之1的剩餘財產差額分配請求權扣除規定，在此範圍內亦不符憲法第7條平等權保障意旨。
+因此，本號判決實際揭示兩項重要問題：一是「擬制遺產產生的稅額應由誰負擔」，二是「擬制遺產應如何計算配偶剩餘財產差額分配請求權扣除額」。
+需強調的是，憲法法庭並未否定死亡前2年贈與財產應併計遺產課稅的制度本身，而是要求立法者補足稅負分配及扣除額計算的規範。憲法法庭要求立法機關於判決公告日起2年內檢討修正，財政部先於114年7月28日發布稽徵作業處理原則，作為修法前的過渡措施，其後完成修法。
+• 三、修法重點：受贈人按財產比例負擔遺產稅115年9月11日修正公布的《遺產及贈與稅法》，將第6條重新調整，增訂受贈人負擔擬制遺產稅額的規定，並另將原本納稅義務人之一「遺囑執行人」刪除，而改為得代辦相關稅務事項：
+1. 第6條第1項：「遺產稅之納稅義務人為繼承人及受遺贈人，無繼承人者，為遺產管理人，並以被繼承人之遺產為限負繳納義務，遺產已移轉或滅失者，按被繼承人死亡時之時價負繳納義務。」
+2. 第6條第3項：「依第十五條第一項併入被繼承人遺產總額課稅之受贈財產，按各受贈財產占遺產總額比例計算之遺產稅額，應以受贈人為納稅義務人，並以受贈財產為限負繳納義務，受贈財產已移轉或滅失者，按被繼承人死亡時之時價負繳納義務，不適用第一項規定。」
+3. 第17條之1第2項：「依第15條第1項第1款併入遺產總額之配偶受贈財產，於計算剩餘財產差額分配請求權扣除數額時，視為被繼承人現存財產。同條第3項並規定，不得以該受贈財產作為履行給付義務之財產。」
+這項規定並非僅限配偶，而是適用於第15條第1項所列的全部受贈對象，包括民法第1138條、第1140條所定各順序繼承人及其配偶。因此，父母死亡前2年贈與子女、孫子女或其他符合第15條規定的親屬，亦可能適用此一稅負分擔制度。
+新法既然以受贈人身分作為課稅依據，受贈人即使拋棄繼承、喪失繼承權，或者本來就不是實際繼承遺產的人，也不因此免除第6條第3項的納稅義務。
+此外，縱使受贈人於贈與人死亡前已將受贈不動產出售，仍須按被繼承人死亡時之時價負繳納義務。依第10條第3項，時價就土地為公告土地現值，房屋為評定標準價格，而非市價。
+• 四、試算範例為具體說明新法，以下以配偶受贈土地為例（甲於115年死亡，依第12條之1規定，適用財政部公告115年發生之繼承案件適用金額）。
+甲於115年11月死亡，遺有配偶乙，以及兩名成年子女丙、丁。甲死亡時，尚有其他遺產價值8,000萬元；另於死亡前1年，曾將一筆土地贈與配偶乙，該土地於甲死亡時的公告土地現值為2,000萬元。
+依《遺產及贈與稅法》第15條規定，該筆土地須併入遺產總額課稅，因此： 遺產總額＝8,000萬元＋2,000萬元＝1億元。 配偶乙受贈財產占遺產總額的比例為： 2,000萬元÷10,000萬元＝20%。
+以下採115年度遺產稅適用金額：免稅額1,333萬元、配偶扣除額553萬元、直系血親卑親屬扣除額每人56萬元、喪葬費扣除額138萬元。另為簡化計算，假設無其他財產、債務、扣除或稅額扣抵事項，且不考慮配偶剩餘財產差額分配請求權扣除額。比較乙未拋棄繼承及拋棄繼承兩種情形：
+• T. ABLE_PLACEHOLDER_1
+本例之情形B，因乙拋棄繼承，依第17條第2項規定，不得扣除配偶扣除額553萬元。乙仍以受贈人身分負擔擬制遺產稅額。
+遺產稅額按115年度適用的累進稅率計算，課稅遺產淨額超過5,621萬元至1億1,242萬元部分，適用15%稅率 情形A：5,621×10%＋(7,864－5,621)×15%＝562.1＋336.45＝898.55萬元。 情形B：562.1＋(8,417－5,621)×15%＝562.1＋419.4＝981.5萬元。
+情形A：配偶未拋棄繼承全案遺產稅額為898.55萬元，其中乙以受贈人身分負擔179.71萬元；其餘718.84萬元，由乙、丙、丁以繼承人身分共同負擔納稅義務。因此，乙具有受贈人與繼承人雙重身分，並不是只須繳納179.71萬元。
+情形B：配偶拋棄繼承全案遺產稅額為981.50萬元，其中乙須以受贈人身分負擔196.30萬元；其餘785.20萬元，則由丙、丁以繼承人身分共同負擔。
+若以修法前的一般納稅義務架構作制度比較，在沒有遺囑執行人的情況下，配偶乙拋棄繼承後，原可能由丙、丁共同承擔全案981.50萬元稅額（惟113年10月28日判決公告後，此一情形已不得再由其他繼承人負擔）；新法則將其中196.30萬元明定由受贈配偶乙負擔。
+綜上，最重要的觀念：遺產稅仍先依整體遺產計算，再按照擬制遺產與其他遺產占遺產總額的比例，劃分受贈人及繼承人的納稅義務。
+參考資料
+1. 憲法法庭113年憲判字第11號判決，113年10月28日。
+2. 財政部臺北國稅局：死亡前2年內贈與財產併計遺產課稅，已修法由「受贈人」按比例負擔稅額，115年10月16日。
+3. 立法院法制局：生前贈與之擬制遺產課稅問題研析，113年11月。
+4. 遺產及贈與稅法（115年9月11日修正公布）。
+5. 財政部114年7月28日台財稅字第11404557320號令。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H986"/>
+  <dimension ref="A1:H987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36498,6 +36498,66 @@
         </is>
       </c>
     </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>916449</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>實價登錄與實價課稅之勾稽</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>2026/10/22</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916449</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:29:08</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>實價登錄、實價課稅、勾稽</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>實價登錄之目的在使不動產交易價格透明化，實價課稅之目的在使不動產課稅公平合理。前者之主管機關為地政機關，後者之主管機關為財稅機關。然，上開二種實價應為一致。
+• (一) 實價登錄：
+1. 申報義務人：(1)成屋買賣：由買方與賣方共同申報。 (2)預售屋買賣：
+• ①起造人或建築業者自行銷售：由起造人或建築業者辦理申報。
+• ②委託不動產經紀業代銷：由不動產經紀業辦理申報。
+2. 申報地點：各地之地政事務所。
+3. 申報期限：(1)成屋買賣：申請所有權移轉登記時，辦理申報。 (2)預售屋買賣：簽訂買賣契約書之日起三十日內，辦理申報。
+4. 申報文件：填具申報書。
+• (二) 實價課稅（指房地合一所得稅）：
+1. 申報義務人：由賣方申報。
+2. 申報地點：各地之國稅局。
+3. 申報期限： (1)成屋買賣：完成所有權移轉登記日之次日起算三十日內申報。 (2)預售屋買賣：預售屋及其坐落基地交易日之次日起算三十日內申報。
+4. 申報文件：填具申報書，檢附契約書影本及其他有關文件。
+• (三) 實價登錄與實價課稅之勾稽：
+1. 地政單位之實價登錄資料應與財稅單位之實價課稅資料相互勾稽。
+2. 現行，實價登錄不必檢附私契影本，實價課稅必須檢附私契影本。為求一致，實價登錄申報亦應檢附私契影本。
+3. 實價登錄之申報實價與實價課稅之申報實價，如有不一致，經查證申報不實，應處以重罰，使申報義務人憚於作假。
+4. 制衡機制： (1)建設公司對於實價登錄之申報實價期望作高，以利於銀行高貸及提高售屋行情。但對於實價課稅之申報實價期望作低，以減少房地合一所得稅。因此，建設公司採取下列作假行為：
+• ①高報實價登錄價格，再以折讓、找補、退款等方式，低報實價課稅價格。
+• ②製造假買賣，高報實價登錄價格，日後解除契約，註銷交易。
+• (2) 就買賣雙方而言，賣方除於民國104年12月31日以前取得之房地外，希望房地交易價格趨低，以減少房地合一所得稅。相對地，買方希望房地交易價格趨高，以減少日後再出售房地之房地合一所得稅。因此，買賣雙方相互制衡結果，最後實價申報價格趨於真正成交價格。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H987"/>
+  <dimension ref="A1:H988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36558,6 +36558,77 @@
         </is>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>916537</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>公寓大廈規約可否訂定罰款？</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>曾榮耀(蘇偉強)</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>2026/10/27</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916537</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:13:33</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>公寓大廈管理條例、公寓大廈規約、私法自治</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>社區住戶違規停車、亂丟垃圾、占用公共空間，管委會可以自行開罰嗎？ 這個問題，法院實務其實有不同見解。
+• 一、案例 甲社區為維護停車秩序，經區分所有權人會議依法決議通過規約，規定住戶違規停車，經勸導仍不改善者，每次罰款3,000元。 住戶乙因多次違規停車，遭管委會要求繳納罰款共3萬元。乙認為管委會不是政府機關，沒有裁罰權限，而且當初並未同意該項規約，因此拒絕繳納。 試問：社區規約訂定的罰款，是否具有法律效力？
+• 二、相關法律規定
+1. 《公寓大廈管理條例》第23條第1項、第2項第4款 「有關公寓大廈、基地或附屬設施之管理使用及其他住戶間相互關係，除法令另有規定外，得以規約定之。」 「規約除應載明專有部分及共用部分範圍外，下列各款事項，非經載明於規約者，不生效力：……四、違反義務之處理方式。……」
+2. 《公寓大廈管理條例》第16條第5項 「住戶違反前四項規定時，管理負責人或管理委員會應予制止或按規約處理，經制止而不遵從者，得報請直轄市、縣（市）主管機關處理。」
+3. 《公寓大廈管理條例》第47條第2款、第49條第1項第4款 「有下列行為之一者，由直轄市、縣（市）主管機關處新臺幣三千元以上一萬五千元以下罰鍰，並得令其限期改善或履行義務、職務；屆期不改善或不履行者，得連續處罰：……二、住戶違反第十六條第一項或第四項規定者。……」 「有下列行為之一者，由直轄市、縣（市）主管機關處新臺幣四萬元以上二十萬元以下罰鍰，並得令其限期改善或履行義務；屆期不改善或不履行者，得連續處罰：……四、住戶違反第十六條第二項或第三項規定者。……」
+4. 《民法》第250條第1項 「當事人得約定債務人於債務不履行時，應支付違約金。」
+5. 《民法》第252條 「約定之違約金額過高者，法院得減至相當之數額。」
+• 三、法院實務見解 針對公寓大廈規約可否訂定罰款，目前司法實務尚無定論，其肯定說及否定說之簡要比較如下：
+• T. ABLE_PLACEHOLDER_1
+註：最高法院目前尚未就此問題正面表態，但曾對否定說的推論提出質疑。最高法院102年度台上字第1751號民事判決（102年9月18日）的案例中，社區規約規定住戶拒絕移除外牆鐵鋁窗等設施者，每10日應支付3,000元「延遲改善懲罰性違約金」；住戶違反規約經制止逾期未改善者，每次應支付1,000元至1萬元懲罰性違約金。原審認為，公寓大廈管理條例第8條第3項已規定住戶違規時應報請主管機關依第49條第1項處理，「即不許規約於報請主管機關依規定處理外，自行訂立處罰條款而為私力救濟」，因而認定條款無效。最高法院則指出，該規定是就住戶違規時管委會應如何處理所為之規定，「是否即限制不得於規約內訂定，區分所有人違反規約時應支付違約金，非無疑義」，原審遽認無效「已有可議」，因此將該部分廢棄發回。陳重見（2024）文亦引用此判決，認為法定處理機制並不排除規約另訂違約金，規約的自律性限制與公權力的他律性限制「應可併行不悖」。
+• 四、兩件值得注意的判決
+• (一) 肯定說：違規占用車道，法院判命給付罰款125萬元 臺灣高等法院臺中分院113年度上易字第302號民事判決（113年10月15日）。 某社區住戶為與管委會抗爭，故意將車輛停放於社區大門車道，致其他住戶車輛無法進出。依規約，占用公共設施經勸導仍不改善者，每小時罰款1萬元，並得連續處罰。 法院認為，法律保留原則僅適用於具有權力服從性質的從屬權力關係，管委會與住戶之間並無從屬關係；該規約條款經區分所有權人會議決議通過，屬於私法自治範疇，不違反強制、禁止規定或公序良俗，具有法律效力。 管委會原請求145萬元，但法院認為依規約須「經勸導仍不改善」才能處罰，因此只計算勸導後的違規時間，核減為125萬元。至於金額是否過高，法院認為得類推適用民法第252條，但審酌違規情節、受影響住戶人數及損害程度後，認為125萬元尚無過高，未予酌減。
+• (二) 否定說：違規停車扣點換算罰款，法院認定部分條款無效 臺灣新北地方法院114年度訴字第3412號民事判決（115年3月31日）。 某社區管委會依規約授權訂定停車場管理辦法，規定違規停車（如超出停車格線）每次扣200點，並可連續扣點；點數不足須以每點1元補足，罰款累積超過3,000元，得聲請支付命令。 法院認為，公寓大廈管理條例已有法定的違規處理機制，社區不得自行創設違反法律保留原則的處罰制度，且本案扣點及金錢處罰手段違反比例原則，因此確認相關處罰性條款無效。 不過，法院並未否定管委會制定一般停車場管理辦法的權限。另須注意，本件為一造辯論判決（管委會未到庭）。
+• 五、案例解析 (一)乙以「未同意規約」為由拒繳，是否有理？
+1. 規約是區分所有權人為增進共同利益、確保良好生活環境，經區分所有權人會議決議的共同遵守事項（公寓大廈管理條例第3條第12款）。甲社區的規約如經區分所有權人會議依第31條規定的出席及同意門檻合法決議，其管理使用的一般規範，原則上對全體區分所有權人及住戶都有拘束力，不以個別區分所有權人同意為必要。
+2. 但就罰款這類金錢負擔，否定說認為，除非獲得全體區分所有權人同意而具有契約性質，否則不得以多數決強行課予未同意者法律所無的義務。依此見解，乙「未同意」的抗辯就有意義。
+• (二) 甲社區的罰款條款是否有效？
+1. 採肯定說：規約已載明違反義務的處理方式，屬私法自治範疇，罰款條款原則有效。法定的主管機關處理機制，也不當然排除規約另訂違約金（最高法院102年度台上字第1751號判決參照）。乙經勸導仍不改善，管委會得請求給付罰款；但規約既以「經勸導仍不改善」為處罰要件，管委會應就勸導事實負舉證責任，且只能就勸導後的違規次數請求。乙並得主張金額過高，請求法院類推適用民法第252條酌減。
+2. 採否定說：「違反義務之處理方式」僅指制止、協調、報請主管機關或訴請法院等程序，罰款條款違反法律保留原則而無效（臺中地院113年度小上字第112號判決參照）。管委會只能制止，或依規定報請主管機關處理、訴請法院為必要的處置。
+• 六、簡要結論 從上述判決可以看出，社區訂定管理規則的權限，與能否自行訂定罰款，是兩個不同問題。另外，也應區分「行政罰鍰」與「私法上的罰款或違約金」。管委會並無行政裁罰權限，但能否透過合法規約約定金錢給付義務，則是目前司法實務存在分歧的問題。 此外，原內政部營建署（現國土管理署）104年2月26日於個案函復中曾指出，住戶違反義務之罰款，除法令另有規定外，應經區分所有權人會議決議後，以規約定之，否則不生效力。不過，這也不代表只要規約有寫，任何罰款都必然有效。仍須考慮規約內容、訂定程序、權限依據、處罰手段及金額是否合理。 因此，不宜直接認定「管委會可以任意罰款」，也不能概括認為「社區罰款一律無效」，仍須依具體規定及個案事實判斷。
+參考資料 一、法院判決
+1. 最高法院102年度台上字第1751號民事判決（102年9月18日）。
+2. 臺灣高等法院臺中分院113年度上易字第302號民事判決（113年10月15日）。
+3. 臺灣臺中地方法院114年度簡上字第454號民事判決（115年1月16日）；同院115年度再易字第9號民事判決（115年6月5日）駁回再審之訴。
+4. 臺灣新北地方法院114年度訴字第3412號民事判決（115年3月31日）。
+5. 臺灣臺中地方法院113年度小上字第112號民事判決（113年8月27日）。
+• 二、學術文獻及官方資料
+1. 陳重見（2024），公寓大廈規約之規範效力，國立政治大學不動產研究中心名家專欄。
+2. 蔡麗雯（2026），公寓大廈規約得否課予住戶「辭讓金」或「罰款」？，《全國律師》，115年3月號，頁105-111。
+3. 陳宏明（2021），公寓大廈自訂罰則之效力，立法院議題研析。
+4. 原內政部營建署（現國土管理署）104年2月26日營署建管字第1042903130號函。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/landnotev3/data/real_estate_articles/articles.xlsx
+++ b/landnotev3/data/real_estate_articles/articles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H988"/>
+  <dimension ref="A1:H989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36629,6 +36629,55 @@
         </is>
       </c>
     </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>916550</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>贈與及遺贈之對照</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>許文昌</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>2026/10/29</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>https://real-estate.get.com.tw/Columns/detail.aspx?no=916550</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:44:42</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>贈與稅、遺贈</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>贈與，指當事人約定，一方以自己之財產無償給與他方，他方允受之契約（民§460）。遺贈，指立遺囑而為贈與。前者於贈與人生前發生效力，後者於遺贈人死後發生效力。
+• (一) 贈與：不動產贈與應辦理贈與所有權移轉登記。對贈與人課徵贈與梲，對受贈人課徵土地增值稅及契稅。被繼承人死亡前二年內贈與下列個人之財產，應於被繼承人死亡時，視為被繼承人之遺產，併入其遺產總額，依遺產及贈與稅法規定徵稅：
+1. 被繼承人之配偶。
+2. 被繼承人依民法第1138條及第1140條規定之各順序繼承人（即直系血親卑親屬、父母、兄弟姊妹、祖父母）。
+3. 前款各順序繼承人之配偶。
+上開擬制遺產之遺產稅，按受贈人財產占遺產總額比例計算稅額，發單向受贈人課徵。
+• (二) 遺贈：不動產遺贈應先辦理繼承登記，再辦理遺贈所有權移轉登記。前者對繼承人及受遺贈人課徵遺產稅（遺贈§6Ⅰ），免徵土地增值稅及契稅。後者對受遺贈人課徵土地增值稅，不徵契稅。受遺贈人申辦遺贈之土地所有權移轉登記，應由繼承人先辦繼承登記後，由繼承人會同受遺贈人申請之；如遺囑另指定有遺囑執行人時，應於辦畢遺囑執行人及繼承登記後，由遺囑執行人會同受遺贈人申請之。前項情形，於繼承人有無不明時，仍應於辦畢遺產管理人登記後，由遺產管理人會同受遺贈人申請之（登§123）。
+• (三) 兩者對照：
+• T. ABLE_PLACEHOLDER_1
+【註】 民：民法。 登：土地登記規則。 遺贈：遺產及贈與稅法。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
